--- a/testbuild/observations-summary.xlsx
+++ b/testbuild/observations-summary.xlsx
@@ -62,7 +62,7 @@
     <t>null#85354-9, null#75367002</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult (extensible)</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1 (extensible)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>
@@ -101,13 +101,13 @@
     <t>vkp-Observation-CFSscore</t>
   </si>
   <si>
-    <t>Vkp VitalSigns Observation - CFS score</t>
+    <t>Vkp Observation - CFS score</t>
   </si>
   <si>
     <t>null#763264000</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
